--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92895</v>
+        <v>92898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>136024097</v>
       </c>
       <c r="B80" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92898</v>
+        <v>92899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92899</v>
+        <v>92904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92904</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93443</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer, Bo karlstens</t>
+          <t>Bo karlstens, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92908</v>
+        <v>92910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92910</v>
+        <v>92911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92911</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93450</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30284-2024 artfynd.xlsx
+++ b/artfynd/A 30284-2024 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136557010</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136557003</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>136557002</v>
       </c>
       <c r="B23" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>136556992</v>
       </c>
       <c r="B54" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>136556993</v>
       </c>
       <c r="B55" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>136556995</v>
       </c>
       <c r="B56" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>136556997</v>
       </c>
       <c r="B57" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>136556998</v>
       </c>
       <c r="B58" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136556999</v>
       </c>
       <c r="B59" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>136557001</v>
       </c>
       <c r="B60" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>136557011</v>
       </c>
       <c r="B61" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
